--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488059_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488059_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6058</v>
+        <v>2.4271</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8304</v>
+        <v>3.6518</v>
       </c>
       <c r="F2" t="n">
         <v>-1.2247</v>
@@ -610,10 +610,10 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9287</v>
+        <v>-0.1074</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0497</v>
+        <v>-0.2284</v>
       </c>
       <c r="U2" t="n">
         <v>0.121</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6227</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.004</v>
+        <v>-0.5112</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3813</v>
+        <v>0.6059</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2176</v>
@@ -922,13 +922,13 @@
         <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8193</v>
+        <v>-0.1019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5285</v>
+        <v>-0.0357</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2908</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>2.4142</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1761</v>
+        <v>-1.2086</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-1.4032</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5032</v>
+        <v>0.1947</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.549</v>
+        <v>-1.3839</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.1614</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.859</v>
+        <v>-1.2224</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6253</v>
+        <v>-1.3179</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0265</v>
+        <v>0.0404</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5988</v>
+        <v>-1.3583</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9237</v>
+        <v>-0.066</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6634</v>
+        <v>-0.2018</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2602</v>
+        <v>0.1358</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7871</v>
+        <v>-0.2211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9435</v>
+        <v>-0.0853</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1564</v>
+        <v>-0.1358</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3104</v>
+        <v>-1.4384</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5051</v>
+        <v>1.1018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1947</v>
+        <v>-2.5402</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3839</v>
+        <v>0.8155</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1614</v>
+        <v>2.0419</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2224</v>
+        <v>-1.2263</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3179</v>
+        <v>3.7424</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0404</v>
+        <v>2.5695</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3583</v>
+        <v>1.1729</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.066</v>
+        <v>-2.9269</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2018</v>
+        <v>-0.5276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1358</v>
+        <v>-2.3993</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.323</v>
+        <v>0.3496</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1872</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1358</v>
+        <v>0.2835</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3728</v>
+        <v>-1.5897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9146</v>
+        <v>-1.1988</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2875</v>
+        <v>-0.3909</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8155</v>
+        <v>-1.549</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0419</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2263</v>
+        <v>-0.859</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7424</v>
+        <v>-0.6253</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5695</v>
+        <v>-0.0265</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1729</v>
+        <v>-0.5988</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9269</v>
+        <v>-0.9237</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5276</v>
+        <v>-0.6634</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3993</v>
+        <v>-0.2602</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4152</v>
+        <v>0.3735</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>0.4176</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5362</v>
+        <v>-0.0441</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0772</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7365</v>
+        <v>-1.6127</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.555</v>
+        <v>-0.5716</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1815</v>
+        <v>-1.0411</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7288</v>
@@ -1234,13 +1234,13 @@
         <v>2.9733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0495</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.393</v>
+        <v>0.3765</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4425</v>
+        <v>-0.3021</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9405</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8694</v>
+        <v>-2.0571</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3811</v>
+        <v>-1.0881</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4883</v>
+        <v>-0.969</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4272</v>
+        <v>-1.5768</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4877</v>
+        <v>0.8204</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.9149</v>
+        <v>-2.3972</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5869</v>
+        <v>0.6068</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6079</v>
+        <v>1.2781</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1948</v>
+        <v>-0.6713</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8403</v>
+        <v>-2.1836</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1201</v>
+        <v>-0.4577</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7201</v>
+        <v>-1.7258</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3787</v>
+        <v>2.7751</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6438</v>
+        <v>-0.5992</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1969</v>
+        <v>-0.2458</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4469</v>
+        <v>-0.3534</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4737</v>
+        <v>-0.674</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6799</v>
+        <v>-3.0379</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6828</v>
+        <v>-2.2126</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9971</v>
+        <v>-0.8253</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5768</v>
+        <v>-3.4272</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8204</v>
+        <v>1.4877</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3972</v>
+        <v>-4.9149</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6068</v>
+        <v>-1.5869</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2781</v>
+        <v>1.6079</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6713</v>
+        <v>-3.1948</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1836</v>
+        <v>-1.8403</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4577</v>
+        <v>-0.1201</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7258</v>
+        <v>-1.7201</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7751</v>
+        <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.222</v>
+        <v>0.4754</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8405</v>
+        <v>0.3654</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3815</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.674</v>
+        <v>-1.4737</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.6663</v>
+        <v>-6.846</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7334</v>
+        <v>-6.9974</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.1514</v>
       </c>
       <c r="G13" t="n">
         <v>-2.89</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3293</v>
+        <v>0.491</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3927</v>
+        <v>0.3434</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0634</v>
+        <v>0.1476</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4737</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.7149</v>
+        <v>-13.1552</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.6759</v>
+        <v>-7.1159</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.039199999999999</v>
+        <v>-6.0392</v>
       </c>
       <c r="G14" t="n">
         <v>-13.4883</v>
@@ -1519,7 +1519,7 @@
         <v>-14.8267</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3601</v>
+        <v>1.360099999999999</v>
       </c>
       <c r="K14" t="n">
         <v>5.6059</v>
@@ -1546,10 +1546,10 @@
         <v>18.8311</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8257000000000001</v>
+        <v>0.7343000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.9739</v>
       </c>
       <c r="U14" t="n">
         <v>-0.2395</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.8652</v>
+        <v>14.1973</v>
       </c>
       <c r="E15" t="n">
-        <v>10.452</v>
+        <v>11.0632</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4132</v>
+        <v>3.1341</v>
       </c>
       <c r="G15" t="n">
         <v>10.9085</v>
@@ -1624,13 +1624,13 @@
         <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2752</v>
+        <v>0.0569</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7781</v>
+        <v>-0.1669</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4972</v>
+        <v>0.2237</v>
       </c>
       <c r="V15" t="n">
         <v>3.4302</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8458</v>
+        <v>4.0015</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1175</v>
+        <v>0.9969</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7283</v>
+        <v>3.0046</v>
       </c>
       <c r="G16" t="n">
         <v>2.1549</v>
@@ -1702,13 +1702,13 @@
         <v>2.1805</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7235</v>
+        <v>0.8792</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5713</v>
+        <v>0.4507</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1522</v>
+        <v>0.4284</v>
       </c>
       <c r="V16" t="n">
         <v>1.7604</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2844</v>
+        <v>3.6672</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6867</v>
+        <v>1.0575</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5977</v>
+        <v>2.6097</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6419</v>
+        <v>1.8051</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5556</v>
+        <v>-1.5468</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1975</v>
+        <v>3.3519</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3489</v>
+        <v>1.6154</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1078</v>
+        <v>-1.5664</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2411</v>
+        <v>3.1818</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2931</v>
+        <v>0.1897</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6634</v>
+        <v>0.0196</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9565</v>
+        <v>0.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7898</v>
+        <v>0.758</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3378</v>
+        <v>0.1222</v>
       </c>
       <c r="U17" t="n">
-        <v>1.452</v>
+        <v>0.6358</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3278</v>
+        <v>2.2935</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.2843</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3278</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5747</v>
+        <v>2.5086</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3444</v>
+        <v>0.5848</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2303</v>
+        <v>1.9238</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8051</v>
+        <v>0.6419</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5468</v>
+        <v>-0.5556</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3519</v>
+        <v>1.1975</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6154</v>
+        <v>0.3489</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5664</v>
+        <v>0.1078</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1818</v>
+        <v>0.2411</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1897</v>
+        <v>0.2931</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0196</v>
+        <v>-0.6634</v>
       </c>
       <c r="O18" t="n">
-        <v>0.17</v>
+        <v>0.9565</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7751</v>
+        <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3345</v>
+        <v>1.014</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5909</v>
+        <v>0.236</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2564</v>
+        <v>0.7781</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2935</v>
+        <v>-1.3278</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2843</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9908</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0526</v>
+        <v>-0.0042</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1865</v>
+        <v>-1.4684</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1338</v>
+        <v>1.4643</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9443</v>
+        <v>2.0706</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2579</v>
+        <v>-1.5778</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3136</v>
+        <v>3.6484</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2414</v>
+        <v>2.5597</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1607</v>
+        <v>2.539</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1857</v>
+        <v>-0.4891</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3386</v>
+        <v>-1.5985</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1529</v>
+        <v>1.1094</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1982</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5841</v>
+        <v>-0.0331</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4368</v>
+        <v>-0.3303</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1473</v>
+        <v>0.2972</v>
       </c>
       <c r="V19" t="n">
-        <v>0.674</v>
+        <v>0.337</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1796</v>
+        <v>-0.3676</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8759</v>
+        <v>-0.8809</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6963</v>
+        <v>0.5132</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0706</v>
+        <v>-0.9443</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5778</v>
+        <v>-1.2579</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6484</v>
+        <v>0.3136</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5597</v>
+        <v>0.2414</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0207</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.539</v>
+        <v>0.1607</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4891</v>
+        <v>-1.1857</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5985</v>
+        <v>-1.3386</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1094</v>
+        <v>0.1529</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3787</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2085</v>
+        <v>0.1009</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7377</v>
+        <v>-0.1312</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4708</v>
+        <v>0.2321</v>
       </c>
       <c r="V20" t="n">
-        <v>0.337</v>
+        <v>0.674</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="21">
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6575</v>
+        <v>-2.4523</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5227</v>
+        <v>-2.2742</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1347</v>
+        <v>-0.1781</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8134</v>
+        <v>-2.8792</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8002</v>
+        <v>-1.473</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0132</v>
+        <v>-1.4062</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3785</v>
+        <v>-2.3744</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2579</v>
+        <v>-1.217</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1205</v>
+        <v>-1.1574</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5048</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4577</v>
+        <v>-0.256</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1073</v>
+        <v>-0.2488</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1716</v>
+        <v>1.784</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6412</v>
+        <v>0.5038</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7967</v>
+        <v>0.1001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1554</v>
+        <v>0.4037</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9405</v>
+        <v>-1.861</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2071</v>
+        <v>-1.861</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7579</v>
+        <v>-2.9115</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1724</v>
+        <v>-2.2358</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5855</v>
+        <v>-0.6756</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8792</v>
+        <v>0.8134</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.473</v>
+        <v>0.8002</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4062</v>
+        <v>0.0132</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3744</v>
+        <v>1.3785</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.217</v>
+        <v>1.2579</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1574</v>
+        <v>0.1205</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5048</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.256</v>
+        <v>-0.4577</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2488</v>
+        <v>-0.1073</v>
       </c>
       <c r="P23" t="n">
-        <v>1.784</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1982</v>
+        <v>0.3872</v>
       </c>
       <c r="T23" t="n">
-        <v>0.202</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0038</v>
+        <v>0.3036</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.861</v>
+        <v>-0.9405</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.861</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.715</v>
+        <v>17.4315</v>
       </c>
       <c r="E24" t="n">
         <v>6.039200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>8.675800000000001</v>
+        <v>11.3924</v>
       </c>
       <c r="G24" t="n">
         <v>13.4882</v>
@@ -2302,7 +2302,7 @@
         <v>14.8482</v>
       </c>
       <c r="K24" t="n">
-        <v>4.267100000000001</v>
+        <v>4.2671</v>
       </c>
       <c r="L24" t="n">
         <v>10.581</v>
@@ -2326,13 +2326,13 @@
         <v>14.8668</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8256000000000003</v>
+        <v>3.5421</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2394999999999998</v>
+        <v>0.2393999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5861</v>
+        <v>3.3026</v>
       </c>
       <c r="V24" t="n">
         <v>4.3658</v>
